--- a/plantillas/79.xlsx
+++ b/plantillas/79.xlsx
@@ -14716,7 +14716,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
       <c r="C564" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         </is>
       </c>
       <c r="C601" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="C610" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         </is>
       </c>
       <c r="C628" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         </is>
       </c>
       <c r="C641" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         </is>
       </c>
       <c r="C727" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         </is>
       </c>
       <c r="C729" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         </is>
       </c>
       <c r="C732" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         </is>
       </c>
       <c r="C734" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         </is>
       </c>
       <c r="C737" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         </is>
       </c>
       <c r="C738" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         </is>
       </c>
       <c r="C811" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         </is>
       </c>
       <c r="C812" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         </is>
       </c>
       <c r="C813" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         </is>
       </c>
       <c r="C814" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
